--- a/human_validation/judge/kor/judge_D006_S004_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S004_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,229 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 직장이랑 학교에서 딱히 말이 안 되는 행동들을 하고 있어서 오게 됐어요. 예를 들면, 영수증을 바닥에 줄지어 늘어놓거나, 계산기를 아홉 번씩 세트로 두드리거나요. 가끔은 복사기 옆에 서서 손을 들고 있다가 누가 괜찮냐고 물어볼 때까지 그러고 있기도 해요. 슬슬 걱정되기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들이, 하고 싶지 않아도 꼭 해야만 할 것 같은 느낌인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네… 뭐 비슷해요. 보통처럼 제가 선택하는 느낌이 아니에요. 그냥 영수증을 줄지어 늘어놓거나 계산기를 아홉 번씩 두드리기 시작하고, 마음 한편으로는 이상하다거나 그만둬야 한다고 생각하면서도 계속하게 돼요. 손 들고 복사기 옆에 서 있는 것도 마찬가지예요—누가 뭐라고 할 때까지는 왜 그러고 있는지 저도 잘 몰라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이런 행동들을 할 때 불안하거나 마음이 안 좋아지시나요, 아니면 특별한 감정 없이 그냥 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 불안이라기보다는요, 적어도 처음엔 아니에요. 그냥 일어나는 것에 더 가까워요, 제가 정말로 생각하기도 전에 영수증을 바닥에 줄지어 늘어놓거나 계산기를 아홉 번씩 두드리고 있거든요. 그러고 나서 누가 눈치챈 후에 좀 창피하거나 걱정될 수는 있어요, 예를 들면 복사기 옆에서 손을 들고 있는데 괜찮냐고 물어볼 때처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동을 하실 때, 그 순간에 그게 말이 안 된다는 걸 알아차리시나요, 아니면 그렇게 해야만 할 것 같은 느낌이 드나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 그 순간에는 뭔가 그렇게 해야만 할 것 같은 느낌이 들어요. 영수증도 그렇고, 그냥 바닥에 늘어놓기 시작하고, 계산기는 아홉 번씩 계속 두드리고요. '이건 말이 안 돼'라고 멈춰서 생각하지는 않아요, 나중에 되거나 누가 눈치챌 때까지는요—예를 들면 복사기 옆에서 손을 들고 있는데 괜찮냐고 물어볼 때처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 아홉 번씩 두드려야만 할 것 같은 느낌이 들 때, 그렇게 하지 않으면 나쁜 일이 생길 거라는 생각이나 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] '나쁜 일이 생길 거야' 같은 건 아닌 것 같아요. 그런 구체적인 생각은 딱히 눈치챈 적이 없어요. 그보다는 그냥 그렇게 해야 할 것 같은 느낌이 들고, 멈추게 되거나 정신이 번쩍 들 때까지 계속하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 강박장애 (D016) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 아홉 번씩 두드리기 시작하기 전에, 그 행동을 하고 나면 풀리는 어떤 신체적인 감각이나 내면의 긴장 같은 게 느껴지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그전에 딱히 신체적인 느낌은 없는 것 같아요, 긴장이 쌓인다거나 그런 것 없이요. 그보다는 그냥 하기 시작해요—영수증을 늘어놓거나, 계산기를 아홉 번씩 두드리거나, 아니면 복사기 옆에 손 들고 서 있거나요—그러고 나서 나중에야 그게 말이 안 된다는 걸 깨달아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 강박장애 (D016) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 시작하기 전에, 머릿속에 떨쳐내기 힘든 특정한 생각이나 이미지, 충동 같은 게 떠오르시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 그런 건 없는 것 같아요. 그 일이 일어나기 전에 머릿속에 특정한 생각이나 이미지를 눈치챈 적은 없어요. 그보다는 그냥 하기 시작하고, 나중에 제가 거기 붙잡혀 있었다는 걸 깨닫는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 하는 동안, 그게 이상하다거나 불필요하다거나 하면 안 될 일이라는 생각이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네… 가끔 하는 동안 그게 이상해 보인다는 걸 어느 정도 깨닫긴 해요, 예를 들면 복사기 옆에서 손을 들고 서 있거나 바닥에 영수증을 늘어놓는 것처럼요. 근데 그 순간에는 바로 멈추지는 않아요. 누가 뭐라고 하거나 제가 정신이 번쩍 들 때까지는 거기에 붙잡혀 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 시작하기 전에, 그 행동을 한 뒤에야 사라지는 것 같은 이상하거나 불편한 신체 감각을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 쌓였다가 그 행동을 하고 나서 사라지는 이상한 몸의 느낌은 눈치챈 적이 없어요. 그보다는 그냥 하기 시작하는 거고, 왜 그러는지는 저도 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 '딱 맞는' 느낌이 들게 하려고, 아니면 정확히 뭔지는 설명 못 해도 뭔가 불편한 일을 막으려고 해야 한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 딱 그런 건 아니에요. 안 하면 나쁜 일이 생길 것 같은 느낌도 아니고, 정확히 '딱 맞는' 느낌을 위한 것도 아니에요. 그냥 별로 말이 안 되는 일들을 하게 되는 거예요, 영수증을 바닥에 늘어놓거나 계산기를 아홉 번씩 두드리는 것처럼요, 그리고 누가 지적해 줄 때까지는 왜 그러는지 저도 잘 몰라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (양극형) (D006)
 인구통계: 성별 남성 / 나이 22 / 직업상태 bookkeeping accounting or auditing clerk / 최종학력 고등학교 졸업
@@ -575,305 +789,48 @@
 증상 지속 기간: 10 months
 추가 요건: psychotic_symptoms and manic_episode occur concurrently, manic_episode is present for the majority of the total duration of the active and residual portions of the illness, delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode
 주호소 증상 코드: S022
-배경 서술: 데메트리오스는 부기 업무를 계속하면서 CPA 과정을 향해 나아가기 위해 저녁 회계 수업에 등록했는데, 이 새로운 구조가 미래 계획을 다듬고 결국 예술가들과 소규모 스튜디오를 도울 수 있게 해주기를 바랐다. 10개월에 걸쳐, 늘어난 압박은 강렬한 생산성에서 임상적으로 유의미한 손상으로 서서히 옮겨가는 것과 맞물렸다. 그는 재무 데이터의 패턴에 대한 고정된 믿음, 생생한 환각 경험, 점점 따라가기 힘든 설명들, 직장과 학교에서의 이상한 행동, 사회적 관심 저하, 그리고 기분이 고양되거나 과민해지고 활동량이 늘고 잠을 거의 안 자고 산만해지며 소프트웨어, 여행 예치금, 미술 재료에 경솔하게 돈을 쓰는 간헐적인 조증 시기를 겪게 되었다. 평소 조용하고 꼼꼼한 성격이었기 때문에 이러한 변화는 처음에는 별난 과로처럼 보였지만, 결국 그의 계정 정리 작업에는 심각한 오류가 생겼고 동급생들은 그의 발표를 이해하기 어려워졌다고 전했다. 그는 중요한 과정 모듈에서 낙제하고 반복해서 고쳐 보려 해도 더는 원장을 안정적으로 완성할 수 없다는 것을 깨달은 뒤 지역 정신건강 클리닉을 통해 스스로 도움을 구했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 직장이랑 학교에서 딱히 말이 안 되는 행동들을 하고 있어서 오게 됐어요. 예를 들면, 영수증을 바닥에 줄지어 늘어놓거나, 계산기를 아홉 번씩 세트로 두드리거나요. 가끔은 복사기 옆에 서서 손을 들고 있다가 누가 괜찮냐고 물어볼 때까지 그러고 있기도 해요. 슬슬 걱정되기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들이, 하고 싶지 않아도 꼭 해야만 할 것 같은 느낌인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네… 뭐 비슷해요. 보통처럼 제가 선택하는 느낌이 아니에요. 그냥 영수증을 줄지어 늘어놓거나 계산기를 아홉 번씩 두드리기 시작하고, 마음 한편으로는 이상하다거나 그만둬야 한다고 생각하면서도 계속하게 돼요. 손 들고 복사기 옆에 서 있는 것도 마찬가지예요—누가 뭐라고 할 때까지는 왜 그러고 있는지 저도 잘 몰라요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이런 행동들을 할 때 불안하거나 마음이 안 좋아지시나요, 아니면 특별한 감정 없이 그냥 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 불안이라기보다는요, 적어도 처음엔 아니에요. 그냥 일어나는 것에 더 가까워요, 제가 정말로 생각하기도 전에 영수증을 바닥에 줄지어 늘어놓거나 계산기를 아홉 번씩 두드리고 있거든요. 그러고 나서 누가 눈치챈 후에 좀 창피하거나 걱정될 수는 있어요, 예를 들면 복사기 옆에서 손을 들고 있는데 괜찮냐고 물어볼 때처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동을 하실 때, 그 순간에 그게 말이 안 된다는 걸 알아차리시나요, 아니면 그렇게 해야만 할 것 같은 느낌이 드나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 그 순간에는 뭔가 그렇게 해야만 할 것 같은 느낌이 들어요. 영수증도 그렇고, 그냥 바닥에 늘어놓기 시작하고, 계산기는 아홉 번씩 계속 두드리고요. '이건 말이 안 돼'라고 멈춰서 생각하지는 않아요, 나중에 되거나 누가 눈치챌 때까지는요—예를 들면 복사기 옆에서 손을 들고 있는데 괜찮냐고 물어볼 때처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 아홉 번씩 두드려야만 할 것 같은 느낌이 들 때, 그렇게 하지 않으면 나쁜 일이 생길 거라는 생각이나 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] '나쁜 일이 생길 거야' 같은 건 아닌 것 같아요. 그런 구체적인 생각은 딱히 눈치챈 적이 없어요. 그보다는 그냥 그렇게 해야 할 것 같은 느낌이 들고, 멈추게 되거나 정신이 번쩍 들 때까지 계속하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 아홉 번씩 두드리기 시작하기 전에, 그 행동을 하고 나면 풀리는 어떤 신체적인 감각이나 내면의 긴장 같은 게 느껴지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그전에 딱히 신체적인 느낌은 없는 것 같아요, 긴장이 쌓인다거나 그런 것 없이요. 그보다는 그냥 하기 시작해요—영수증을 늘어놓거나, 계산기를 아홉 번씩 두드리거나, 아니면 복사기 옆에 손 들고 서 있거나요—그러고 나서 나중에야 그게 말이 안 된다는 걸 깨달아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 시작하기 전에, 머릿속에 떨쳐내기 힘든 특정한 생각이나 이미지, 충동 같은 게 떠오르시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 그런 건 없는 것 같아요. 그 일이 일어나기 전에 머릿속에 특정한 생각이나 이미지를 눈치챈 적은 없어요. 그보다는 그냥 하기 시작하고, 나중에 제가 거기 붙잡혀 있었다는 걸 깨닫는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 하는 동안, 그게 이상하다거나 불필요하다거나 하면 안 될 일이라는 생각이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네… 가끔 하는 동안 그게 이상해 보인다는 걸 어느 정도 깨닫긴 해요, 예를 들면 복사기 옆에서 손을 들고 서 있거나 바닥에 영수증을 늘어놓는 것처럼요. 근데 그 순간에는 바로 멈추지는 않아요. 누가 뭐라고 하거나 제가 정신이 번쩍 들 때까지는 거기에 붙잡혀 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 시작하기 전에, 그 행동을 한 뒤에야 사라지는 것 같은 이상하거나 불편한 신체 감각을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 아니요, 그런 건 없는 것 같아요. 쌓였다가 그 행동을 하고 나서 사라지는 이상한 몸의 느낌은 눈치챈 적이 없어요. 그보다는 그냥 하기 시작하는 거고, 왜 그러는지는 저도 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 영수증을 줄지어 놓거나 계산기를 두드리는 것 같은 이런 행동들을 '딱 맞는' 느낌이 들게 하려고, 아니면 정확히 뭔지는 설명 못 해도 뭔가 불편한 일을 막으려고 해야 한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 딱 그런 건 아니에요. 안 하면 나쁜 일이 생길 것 같은 느낌도 아니고, 정확히 '딱 맞는' 느낌을 위한 것도 아니에요. 그냥 별로 말이 안 되는 일들을 하게 되는 거예요, 영수증을 바닥에 늘어놓거나 계산기를 아홉 번씩 두드리는 것처럼요, 그리고 누가 지적해 줄 때까지는 왜 그러는지 저도 잘 몰라요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+배경 서술: 데메트리오스는 부기 업무를 계속하면서 CPA 과정을 향해 나아가기 위해 저녁 회계 수업에 등록했는데, 이 새로운 구조가 미래 계획을 다듬고 결국 예술가들과 소규모 스튜디오를 도울 수 있게 해주기를 바랐다. 10개월에 걸쳐, 늘어난 압박은 강렬한 생산성에서 임상적으로 유의미한 손상으로 서서히 옮겨가는 것과 맞물렸다. 그는 재무 데이터의 패턴에 대한 고정된 믿음, 생생한 환각 경험, 점점 따라가기 힘든 설명들, 직장과 학교에서의 이상한 행동, 사회적 관심 저하, 그리고 기분이 고양되거나 과민해지고 활동량이 늘고 잠을 거의 안 자고 산만해지며 소프트웨어, 여행 예치금, 미술 재료에 경솔하게 돈을 쓰는 간헐적인 조증 시기를 겪게 되었다. 평소 조용하고 꼼꼼한 성격이었기 때문에 이러한 변화는 처음에는 별난 과로처럼 보였지만, 결국 그의 계정 정리 작업에는 심각한 오류가 생겼고 동급생들은 그의 발표를 이해하기 어려워졌다고 전했다. 그는 중요한 과정 모듈에서 낙제하고 반복해서 고쳐 보려 해도 더는 원장을 안정적으로 완성할 수 없다는 것을 깨달은 뒤 지역 정신건강 클리닉을 통해 스스로 도움을 구했다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S021 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
+  - S022 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+  - S041 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
+        </is>
+      </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42.9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42.9)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: 없음
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S004_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S004_P002__qwen3-235b_kor.xlsx
@@ -775,6 +775,11 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -826,11 +831,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S004_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S004_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.04</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
